--- a/results/Int All Data -0.0/Rando_3_permute.xlsx
+++ b/results/Int All Data -0.0/Rando_3_permute.xlsx
@@ -440,947 +440,947 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7985657399450503</v>
+        <v>0.786030186030186</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7962987618160031</v>
+        <v>0.8000338896890621</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7918604228949057</v>
+        <v>0.797820166785684</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7963943791529998</v>
+        <v>0.7990740852809819</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7979617772721221</v>
+        <v>0.7896733276043622</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8004696142627177</v>
+        <v>0.790300286852011</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.799070454242868</v>
+        <v>0.7796153520291451</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7893562169424239</v>
+        <v>0.7796153520291451</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7911414773483738</v>
+        <v>0.7850401229711574</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.791336343060481</v>
+        <v>0.7836409629513078</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.791336343060481</v>
+        <v>0.7800474455646869</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7971508454267076</v>
+        <v>0.8047663426973772</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7960421684559615</v>
+        <v>0.8057067815688506</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7956330714951405</v>
+        <v>0.8004272521513901</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7904721559893974</v>
+        <v>0.798087653260067</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7907856356132219</v>
+        <v>0.8090364435192021</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7913399740985948</v>
+        <v>0.8052746880333087</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7903269144648455</v>
+        <v>0.8075416661623558</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.783889083889084</v>
+        <v>0.805465922707302</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7777151087495915</v>
+        <v>0.8084361118843877</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7794313794313794</v>
+        <v>0.8087229638953777</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7805400564021254</v>
+        <v>0.8045291148739424</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.789871824354583</v>
+        <v>0.8093305576064197</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7936335798404763</v>
+        <v>0.8086309775964948</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7942605390881253</v>
+        <v>0.80793139758657</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8030609651299306</v>
+        <v>0.7786131855097372</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8030609651299306</v>
+        <v>0.7810980259256122</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8072088210019244</v>
+        <v>0.7733566526669975</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8087035983587707</v>
+        <v>0.7698127594679319</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8051597051597053</v>
+        <v>0.7707531983394053</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8061001440311786</v>
+        <v>0.76298882850607</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8098618995170719</v>
+        <v>0.7726110795076312</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8026712337057165</v>
+        <v>0.7866450418174555</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8166858304789339</v>
+        <v>0.7861136999068034</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8129966957553165</v>
+        <v>0.793033248205662</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8109475799130972</v>
+        <v>0.7952276055724332</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8116471599230219</v>
+        <v>0.7884726643347333</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8119606395468464</v>
+        <v>0.7922344198206267</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8056184263080814</v>
+        <v>0.7967417484658864</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.80868060178405</v>
+        <v>0.796355648079786</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7867370281163385</v>
+        <v>0.8065286065286066</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7758378620447586</v>
+        <v>0.7985959985959986</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7738347393519808</v>
+        <v>0.7963411239273308</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7710860434998366</v>
+        <v>0.7953583229445298</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7710860434998366</v>
+        <v>0.7932099587272001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7792292516430448</v>
+        <v>0.7810302465474879</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7785066750583992</v>
+        <v>0.7834424662010868</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7755171203447065</v>
+        <v>0.7886953680057128</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.775757979206255</v>
+        <v>0.7648709165950545</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7739497222255842</v>
+        <v>0.7640260950605778</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7659444935307005</v>
+        <v>0.7655438689921449</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7619418791832585</v>
+        <v>0.7612507715955992</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7605197225886882</v>
+        <v>0.764665157768606</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7545406131613028</v>
+        <v>0.7660643177884557</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7545406131613028</v>
+        <v>0.7591677660643178</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7445358928117549</v>
+        <v>0.7591677660643178</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7473802060008956</v>
+        <v>0.7686217789666066</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7480071652485445</v>
+        <v>0.7661865627382869</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7392297357814599</v>
+        <v>0.755769114389804</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7034204379031965</v>
+        <v>0.7597027390130838</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6971738420014282</v>
+        <v>0.7576536231708646</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6971508454267075</v>
+        <v>0.762038706866293</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6902809213154041</v>
+        <v>0.7599895910240737</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6826847895813413</v>
+        <v>0.755448372689752</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7076409145374662</v>
+        <v>0.7526427905738251</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7268975200009683</v>
+        <v>0.7538325607291125</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7260563295046054</v>
+        <v>0.745338352234904</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7295312329795088</v>
+        <v>0.7336984543881095</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7255746117815083</v>
+        <v>0.7336984543881095</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7224131879304293</v>
+        <v>0.7333849747642851</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7181697147214389</v>
+        <v>0.7285835320318079</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7227302985923676</v>
+        <v>0.7144430592706454</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7095980440808027</v>
+        <v>0.6962237203616514</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7095980440808027</v>
+        <v>0.6871751733820699</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7021701504460125</v>
+        <v>0.6868616937582455</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6944057806126771</v>
+        <v>0.6880199949165466</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6943331598504012</v>
+        <v>0.6776824294065673</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6945510221372291</v>
+        <v>0.6907093838128321</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6854153302429165</v>
+        <v>0.6868786386027765</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6896164413405792</v>
+        <v>0.6799288316529696</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6889168613306544</v>
+        <v>0.6842715532370705</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6926289926289926</v>
+        <v>0.6684910615945099</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6880793018724054</v>
+        <v>0.663701722322412</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.685762699555803</v>
+        <v>0.6385822006511661</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6838818218128563</v>
+        <v>0.6434211641108193</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6913593396352017</v>
+        <v>0.6429164498130016</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6974606940124182</v>
+        <v>0.6429164498130016</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6941806562496218</v>
+        <v>0.6451555899831762</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6970249694387625</v>
+        <v>0.6360574188160395</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7053206811827502</v>
+        <v>0.6001379794483243</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7053206811827502</v>
+        <v>0.5992931579138475</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7203761755485893</v>
+        <v>0.5997978722116653</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7127122644364023</v>
+        <v>0.5957190060638337</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7232931095000061</v>
+        <v>0.5946599532806429</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7292455913145568</v>
+        <v>0.5577589232761646</v>
       </c>
     </row>
     <row r="97">
@@ -1390,597 +1390,597 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7276322000459932</v>
+        <v>0.5525750111957008</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7287178804420184</v>
+        <v>0.6099199961268926</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.7227387710146331</v>
+        <v>0.602302078164147</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7190460052529019</v>
+        <v>0.6348071313588555</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.7265198920371334</v>
+        <v>0.6253434356882632</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.7288473874680771</v>
+        <v>0.6290591980247153</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7288473874680771</v>
+        <v>0.5375618789411893</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.7241185654978759</v>
+        <v>0.5379479793272897</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.7178223454085523</v>
+        <v>0.5382614589511141</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.7200893235375994</v>
+        <v>0.5116895220343496</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.7207889035475242</v>
+        <v>0.5114716597475218</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.7207889035475242</v>
+        <v>0.5250844216361458</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.7207889035475242</v>
+        <v>0.5401810677672747</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.7226927778651917</v>
+        <v>0.5378644654506723</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.7173454690696071</v>
+        <v>0.5240411033514482</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.7206714999818449</v>
+        <v>0.5284334491231043</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.7123987848125779</v>
+        <v>0.5303639510536062</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.6548528824390893</v>
+        <v>0.5298096125682332</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.6548528824390893</v>
+        <v>0.5461517047723944</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.6685697340869755</v>
+        <v>0.5448021689401</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.668256254463151</v>
+        <v>0.5293811500708052</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.4978020115951151</v>
+        <v>0.5068299826920516</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4978020115951151</v>
+        <v>0.5237954031057479</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4989603127534162</v>
+        <v>0.510269786131855</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4996598927633411</v>
+        <v>0.5139625518935864</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4994916546640685</v>
+        <v>0.4898669829704313</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4994916546640685</v>
+        <v>0.4898669829704313</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.499178175040244</v>
+        <v>0.4715798646833129</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5012769150700185</v>
+        <v>0.4673133948996018</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4948814466055845</v>
+        <v>0.4642935815349608</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4987194538918677</v>
+        <v>0.4912661429902809</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4987194538918677</v>
+        <v>0.4815531160358746</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4993960373270718</v>
+        <v>0.4960917926435168</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5003364761985452</v>
+        <v>0.4858123237433582</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4999503758124448</v>
+        <v>0.4925103787172753</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.499178175040244</v>
+        <v>0.4889713269023614</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4999273792377241</v>
+        <v>0.4207659069728035</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5003134796238244</v>
+        <v>0.4207659069728035</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4999273792377241</v>
+        <v>0.4205020515365343</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4999273792377241</v>
+        <v>0.4209837692596313</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5003134796238244</v>
+        <v>0.4180172111206594</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5003134796238244</v>
+        <v>0.371489088730468</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5</v>
+        <v>0.4283233076336525</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5</v>
+        <v>0.4283233076336525</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5</v>
+        <v>0.4922937267764854</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5</v>
+        <v>0.4797472797472798</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5</v>
+        <v>0.4865288485978141</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5</v>
+        <v>0.4804202321443701</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5</v>
+        <v>0.4741433775916534</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5</v>
+        <v>0.4837765217075561</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5003134796238244</v>
+        <v>0.4853669164013992</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5003134796238244</v>
+        <v>0.4854395371636751</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5003134796238244</v>
+        <v>0.4854395371636751</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5003134796238244</v>
+        <v>0.4894687791239516</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5003134796238244</v>
+        <v>0.4901223659844349</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4995412788516237</v>
+        <v>0.49925079580252</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4997821377131722</v>
+        <v>0.49925079580252</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4991551784655233</v>
+        <v>0.49925079580252</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4987690780794229</v>
+        <v>0.4999273792377241</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5</v>
+        <v>0.4999273792377241</v>
       </c>
     </row>
   </sheetData>
